--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1701,6 +1701,120 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123506663</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57815</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>538531</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6354848</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1701,6 +1701,124 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124784691</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57847</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>538602</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6354907</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -1706,7 +1706,7 @@
         <v>124784691</v>
       </c>
       <c r="B10" t="n">
-        <v>57847</v>
+        <v>57961</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,6 +1819,115 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125746780</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58019</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>538507</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6354846</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,12 +1450,7 @@
         <v>99253693</v>
       </c>
       <c r="B8" t="n">
-        <v>56717</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,10 +1498,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>538515.3464311194</v>
+        <v>538516</v>
       </c>
       <c r="R8" t="n">
-        <v>6354864.932380745</v>
+        <v>6354865</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1536,19 +1531,9 @@
           <t>2022-03-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-03-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1928,6 +1913,119 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125922461</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57979</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103008</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ärtsångare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Curruca curruca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hagbacken, Ålefors, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>538532</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6354854</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marie Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>99253693</v>
       </c>
       <c r="B8" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>125922461</v>
       </c>
       <c r="B12" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -1809,7 +1809,7 @@
         <v>125746780</v>
       </c>
       <c r="B11" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>99253693</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>125746780</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>125922461</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>99253693</v>
       </c>
       <c r="B8" t="n">
-        <v>57981</v>
+        <v>57985</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>125746780</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>125922461</v>
       </c>
       <c r="B12" t="n">
-        <v>57981</v>
+        <v>57985</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40640-2020 artfynd.xlsx
+++ b/artfynd/A 40640-2020 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>99253693</v>
       </c>
       <c r="B8" t="n">
-        <v>57985</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>125922461</v>
       </c>
       <c r="B12" t="n">
-        <v>57985</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
